--- a/calculations.xlsx
+++ b/calculations.xlsx
@@ -274,7 +274,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -560,13 +560,13 @@
   <dimension ref="A1:K28"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="24.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="22.95"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="30.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="19.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="20.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="19.1"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="19.48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="14.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="16.13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="17.91"/>
   </cols>
   <sheetData>
@@ -992,7 +992,6 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="0"/>
       <c r="C12" s="21"/>
       <c r="D12" s="21"/>
       <c r="E12" s="21"/>
@@ -1006,7 +1005,7 @@
         <v>22</v>
       </c>
       <c r="C13" s="23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D13" s="24"/>
       <c r="E13" s="25"/>
@@ -1033,11 +1032,11 @@
       </c>
       <c r="D15" s="8" t="n">
         <f aca="false">C15*C13</f>
-        <v>16.5</v>
+        <v>27.5</v>
       </c>
       <c r="E15" s="26" t="n">
         <f aca="false">I2*C13</f>
-        <v>0.790367325000002</v>
+        <v>1.317278875</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1050,11 +1049,11 @@
       </c>
       <c r="D16" s="12" t="n">
         <f aca="false">C16*C13</f>
-        <v>32.159325</v>
+        <v>53.598875</v>
       </c>
       <c r="E16" s="26" t="n">
         <f aca="false">I3*C13</f>
-        <v>1.54003317560813</v>
+        <v>2.56672195934688</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1067,11 +1066,11 @@
       </c>
       <c r="D17" s="15" t="n">
         <f aca="false">C17*C13</f>
-        <v>61.8822897825</v>
+        <v>103.1371496375</v>
       </c>
       <c r="E17" s="26" t="n">
         <f aca="false">I4*C13</f>
-        <v>2.09847717335656</v>
+        <v>3.49746195559426</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1084,11 +1083,11 @@
       </c>
       <c r="D18" s="12" t="n">
         <f aca="false">C18*C13</f>
-        <v>118.299449236163</v>
+        <v>197.165748726939</v>
       </c>
       <c r="E18" s="26" t="n">
         <f aca="false">I5*C13</f>
-        <v>3.15765896534614</v>
+        <v>5.26276494224357</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1101,11 +1100,11 @@
       </c>
       <c r="D19" s="15" t="n">
         <f aca="false">C19*C13</f>
-        <v>225.384859595161</v>
+        <v>375.641432658602</v>
       </c>
       <c r="E19" s="26" t="n">
         <f aca="false">I6*C13</f>
-        <v>5.16733120259161</v>
+        <v>8.61221867098601</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1118,11 +1117,11 @@
       </c>
       <c r="D20" s="12" t="n">
         <f aca="false">C20*C13</f>
-        <v>428.643676997576</v>
+        <v>714.406128329293</v>
       </c>
       <c r="E20" s="26" t="n">
         <f aca="false">I7*C13</f>
-        <v>8.98116739008394</v>
+        <v>14.9686123168066</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1135,11 +1134,11 @@
       </c>
       <c r="D21" s="15" t="n">
         <f aca="false">C21*C13</f>
-        <v>814.449238309099</v>
+        <v>1357.41539718183</v>
       </c>
       <c r="E21" s="26" t="n">
         <f aca="false">I8*C13</f>
-        <v>16.2195233058408</v>
+        <v>27.0325388430681</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1152,11 +1151,11 @@
       </c>
       <c r="D22" s="12" t="n">
         <f aca="false">C22*C13</f>
-        <v>1546.7467742345</v>
+        <v>2577.91129039083</v>
       </c>
       <c r="E22" s="26" t="n">
         <f aca="false">I9*C13</f>
-        <v>29.9579944454034</v>
+        <v>49.929990742339</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1169,11 +1168,11 @@
       </c>
       <c r="D23" s="15" t="n">
         <f aca="false">C23*C13</f>
-        <v>2936.7207271745</v>
+        <v>4894.53454529084</v>
       </c>
       <c r="E23" s="26" t="n">
         <f aca="false">I10*C13</f>
-        <v>56.0343669024747</v>
+        <v>93.3906115041245</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1186,11 +1185,11 @@
       </c>
       <c r="D24" s="19" t="n">
         <f aca="false">C24*C13</f>
-        <v>5575.03028724993</v>
+        <v>9291.71714541654</v>
       </c>
       <c r="E24" s="26" t="n">
         <f aca="false">I11*C13</f>
-        <v>122.029340830968</v>
+        <v>203.38223471828</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
